--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAG-Parser-v2\FRS_filtered\Nov\Fmn D Nov\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E674D2-2D3E-4233-A67A-A28D45E0DAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC967E-7D94-4875-937A-30990647E68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -3593,7 +3593,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -3760,7 +3760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3779,19 +3779,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3806,14 +3794,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4122,18 +4128,18 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="12"/>
-    <col min="2" max="2" width="13.5" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="18" style="12" customWidth="1"/>
-    <col min="7" max="7" width="14" style="12" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="18" style="12" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="67.83203125" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="9.33203125" style="12"/>
+    <col min="1" max="1" width="9.33203125" style="8"/>
+    <col min="2" max="2" width="13.5" style="8" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="18" style="8" customWidth="1"/>
+    <col min="7" max="7" width="14" style="8" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="18" style="19" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="67.83203125" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9.33203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
@@ -4161,10 +4167,10 @@
       <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -4173,16 +4179,16 @@
     </row>
     <row r="2" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>146</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -4194,10 +4200,10 @@
       <c r="H2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="12">
         <v>45377</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -4205,32 +4211,32 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="13">
         <v>45057</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>93</v>
       </c>
       <c r="K3" s="4" t="s">
@@ -4238,32 +4244,32 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="9" t="s">
         <v>146</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="9" t="s">
         <v>48</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="14">
         <v>44810</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>93</v>
       </c>
       <c r="K4" s="5" t="s">
@@ -4271,17 +4277,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -4293,10 +4299,10 @@
       <c r="H5" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="12">
         <v>45736</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="6" t="s">
         <v>97</v>
       </c>
       <c r="K5" s="4" t="s">
@@ -4304,32 +4310,32 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="9" t="s">
         <v>146</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="9" t="s">
         <v>49</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="14">
         <v>44816</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="6" t="s">
         <v>93</v>
       </c>
       <c r="K6" s="5" t="s">
@@ -4337,32 +4343,32 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="9" t="s">
         <v>49</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="12">
         <v>45743</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>97</v>
       </c>
       <c r="K7" s="5" t="s">
@@ -4370,17 +4376,17 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="9" t="s">
         <v>146</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -4392,10 +4398,10 @@
       <c r="H8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="12">
         <v>45796</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="6" t="s">
         <v>93</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -4403,32 +4409,32 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="9" t="s">
         <v>52</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="13">
         <v>44569</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="6" t="s">
         <v>97</v>
       </c>
       <c r="K9" s="5" t="s">
@@ -4436,32 +4442,32 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="9" t="s">
         <v>52</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="14">
         <v>45708</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>93</v>
       </c>
       <c r="K10" s="4" t="s">
@@ -4469,17 +4475,17 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -4491,10 +4497,10 @@
       <c r="H11" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="12">
         <v>45799</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="6" t="s">
         <v>93</v>
       </c>
       <c r="K11" s="4" t="s">
@@ -4502,32 +4508,32 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="9" t="s">
         <v>49</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="15">
         <v>45936</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K12" s="4" t="s">
@@ -4535,32 +4541,32 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="9" t="s">
         <v>50</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="15">
         <v>45936</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K13" s="4" t="s">
@@ -4568,32 +4574,32 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="9" t="s">
         <v>51</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="15">
         <v>45708</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K14" s="4" t="s">
@@ -4601,17 +4607,17 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -4623,10 +4629,10 @@
       <c r="H15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="15">
         <v>45796</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K15" s="4" t="s">
@@ -4634,17 +4640,17 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
@@ -4659,7 +4665,7 @@
       <c r="I16" s="16">
         <v>45736</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K16" s="4" t="s">
@@ -4667,17 +4673,17 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -4689,10 +4695,10 @@
       <c r="H17" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="15">
         <v>45922</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K17" s="5" t="s">
@@ -4700,32 +4706,32 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="9" t="s">
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -4733,32 +4739,32 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K19" s="4" t="s">
@@ -4766,23 +4772,23 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="9" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -4791,7 +4797,7 @@
       <c r="I20" s="17">
         <v>45811</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K20" s="4" t="s">
@@ -4799,32 +4805,32 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="9" t="s">
         <v>74</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="15">
         <v>45740</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K21" s="5" t="s">
@@ -4832,32 +4838,32 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="9" t="s">
         <v>75</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="15">
         <v>45657</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K22" s="4" t="s">
@@ -4865,32 +4871,32 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="9" t="s">
         <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="15">
         <v>45573</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K23" s="4" t="s">
@@ -4898,32 +4904,32 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13" t="s">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="9" t="s">
         <v>77</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="15">
         <v>45657</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K24" s="5" t="s">
@@ -4931,32 +4937,32 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="9" t="s">
         <v>74</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="15">
         <v>44816</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K25" s="4" t="s">
@@ -4964,32 +4970,32 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13" t="s">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="9" t="s">
         <v>75</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="15">
         <v>45831</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="6" t="s">
         <v>90</v>
       </c>
       <c r="K26" s="5" t="s">
@@ -4997,32 +5003,32 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="9" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="15">
         <v>45353</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K27" s="4" t="s">
@@ -5030,32 +5036,32 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="9" t="s">
         <v>51</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="15">
         <v>45754</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="6" t="s">
         <v>138</v>
       </c>
       <c r="K28" s="4" t="s">
@@ -5063,23 +5069,23 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="9" t="s">
         <v>51</v>
       </c>
       <c r="H29" s="5" t="s">
@@ -5088,7 +5094,7 @@
       <c r="I29" s="17">
         <v>45790</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K29" s="4" t="s">
@@ -5096,32 +5102,32 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13" t="s">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="9" t="s">
         <v>78</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="15">
         <v>45916</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K30" s="5" t="s">
@@ -5129,63 +5135,63 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="9" t="s">
         <v>78</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="15">
         <v>45950</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" s="6" t="s">
         <v>0</v>
       </c>
       <c r="K31" s="5"/>
     </row>
     <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13" t="s">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="9" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="15">
         <v>45903</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K32" s="5" t="s">
@@ -5193,32 +5199,32 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="9" t="s">
         <v>74</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="15">
         <v>45923</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="6" t="s">
         <v>109</v>
       </c>
       <c r="K33" s="5" t="s">
@@ -5226,258 +5232,258 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H35" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="15">
         <v>45831</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="K35" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H36" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="15">
         <v>45353</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="J36" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="K36" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="15">
         <v>45740</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K37" s="13" t="s">
+      <c r="K37" s="9" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13" t="s">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="15">
         <v>45657</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K38" s="13" t="s">
+      <c r="K38" s="9" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="15">
         <v>45831</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="J39" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K39" s="13" t="s">
+      <c r="K39" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13" t="s">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="15">
         <v>45353</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="J40" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="9" t="s">
         <v>70</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="15">
         <v>45754</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="J41" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K41" s="13" t="s">
+      <c r="K41" s="9" t="s">
         <v>153</v>
       </c>
     </row>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC967E-7D94-4875-937A-30990647E68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE30336-DFD1-473B-ABA1-113137A83A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-15720" windowWidth="28800" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="FR" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -3593,7 +3593,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -3760,7 +3760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3794,32 +3794,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4126,23 +4129,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD5C46C-B07C-42BA-9996-0A0B735859A2}">
   <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="8"/>
-    <col min="2" max="2" width="13.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="8" customWidth="1"/>
     <col min="6" max="6" width="18" style="8" customWidth="1"/>
     <col min="7" max="7" width="14" style="8" customWidth="1"/>
     <col min="8" max="8" width="30.6640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="18" style="19" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="67.83203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="8" customWidth="1"/>
+    <col min="11" max="11" width="67.77734375" style="8" customWidth="1"/>
     <col min="12" max="16384" width="9.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -4177,8 +4180,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
       <c r="B2" s="9" t="s">
         <v>26</v>
       </c>
@@ -4210,8 +4215,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
+    <row r="3" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
+        <v>2</v>
+      </c>
       <c r="B3" s="9" t="s">
         <v>26</v>
       </c>
@@ -4243,8 +4250,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
+    <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
       <c r="B4" s="9" t="s">
         <v>26</v>
       </c>
@@ -4276,8 +4285,10 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
+    <row r="5" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
+        <v>4</v>
+      </c>
       <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
@@ -4309,8 +4320,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
+    <row r="6" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>26</v>
       </c>
@@ -4342,8 +4355,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>6</v>
+      </c>
       <c r="B7" s="9" t="s">
         <v>26</v>
       </c>
@@ -4375,8 +4390,10 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
+    <row r="8" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
       <c r="B8" s="9" t="s">
         <v>26</v>
       </c>
@@ -4408,8 +4425,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
+    <row r="9" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>8</v>
+      </c>
       <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
@@ -4441,8 +4460,10 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
+    <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
       <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
@@ -4474,8 +4495,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
+    <row r="11" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
+        <v>10</v>
+      </c>
       <c r="B11" s="9" t="s">
         <v>26</v>
       </c>
@@ -4507,8 +4530,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
+    <row r="12" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
       <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
@@ -4540,8 +4565,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
+    <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <v>12</v>
+      </c>
       <c r="B13" s="9" t="s">
         <v>26</v>
       </c>
@@ -4573,8 +4600,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
+    <row r="14" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>26</v>
       </c>
@@ -4606,8 +4635,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
+    <row r="15" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
+        <v>14</v>
+      </c>
       <c r="B15" s="9" t="s">
         <v>26</v>
       </c>
@@ -4639,8 +4670,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
       <c r="B16" s="9" t="s">
         <v>26</v>
       </c>
@@ -4672,8 +4705,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
+        <v>16</v>
+      </c>
       <c r="B17" s="9" t="s">
         <v>26</v>
       </c>
@@ -4705,8 +4740,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
       <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
@@ -4738,8 +4775,10 @@
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
+        <v>18</v>
+      </c>
       <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
@@ -4771,8 +4810,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
+    <row r="20" spans="1:11" ht="66" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
       <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
@@ -4804,8 +4845,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="20">
+        <v>20</v>
+      </c>
       <c r="B21" s="9" t="s">
         <v>26</v>
       </c>
@@ -4837,8 +4880,10 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
+    <row r="22" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
       <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
@@ -4870,8 +4915,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
+    <row r="23" spans="1:11" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="20">
+        <v>22</v>
+      </c>
       <c r="B23" s="9" t="s">
         <v>26</v>
       </c>
@@ -4903,8 +4950,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
       <c r="B24" s="9" t="s">
         <v>26</v>
       </c>
@@ -4936,8 +4985,10 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
+    <row r="25" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
+        <v>24</v>
+      </c>
       <c r="B25" s="9" t="s">
         <v>26</v>
       </c>
@@ -4969,8 +5020,10 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
       <c r="B26" s="9" t="s">
         <v>26</v>
       </c>
@@ -5002,8 +5055,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
+    <row r="27" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A27" s="20">
+        <v>26</v>
+      </c>
       <c r="B27" s="9" t="s">
         <v>26</v>
       </c>
@@ -5035,8 +5090,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
       <c r="B28" s="9" t="s">
         <v>26</v>
       </c>
@@ -5068,8 +5125,10 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
+    <row r="29" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A29" s="20">
+        <v>28</v>
+      </c>
       <c r="B29" s="9" t="s">
         <v>26</v>
       </c>
@@ -5101,8 +5160,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
       <c r="B30" s="9" t="s">
         <v>26</v>
       </c>
@@ -5134,8 +5195,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="20">
+        <v>30</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>26</v>
       </c>
@@ -5165,8 +5228,10 @@
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
+    <row r="32" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
       <c r="B32" s="9" t="s">
         <v>26</v>
       </c>
@@ -5198,8 +5263,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="20">
+        <v>32</v>
+      </c>
       <c r="B33" s="9" t="s">
         <v>26</v>
       </c>
@@ -5231,8 +5298,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
       <c r="B34" s="9" t="s">
         <v>26</v>
       </c>
@@ -5256,8 +5325,10 @@
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="20">
+        <v>34</v>
+      </c>
       <c r="B35" s="9" t="s">
         <v>26</v>
       </c>
@@ -5289,8 +5360,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
       <c r="B36" s="9" t="s">
         <v>26</v>
       </c>
@@ -5322,8 +5395,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="20">
+        <v>36</v>
+      </c>
       <c r="B37" s="9" t="s">
         <v>26</v>
       </c>
@@ -5355,8 +5430,10 @@
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -5388,8 +5465,10 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="20">
+        <v>38</v>
+      </c>
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -5421,8 +5500,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -5454,8 +5535,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="20">
+        <v>40</v>
+      </c>
       <c r="B41" s="9" t="s">
         <v>26</v>
       </c>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE30336-DFD1-473B-ABA1-113137A83A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E790D7B8-DC0A-4A22-8651-060B543F311A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-15720" windowWidth="28800" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-15195" windowWidth="28800" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FR" sheetId="2" r:id="rId1"/>
@@ -125,18 +125,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Type of Veh</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF050505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Tk BA No</t>
     </r>
   </si>
@@ -3586,6 +3574,9 @@
   </si>
   <si>
     <t>Under FR</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -4150,25 +4141,25 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>16</v>
@@ -4177,7 +4168,7 @@
         <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="52.8" x14ac:dyDescent="0.25">
@@ -4185,10 +4176,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>18</v>
@@ -4197,13 +4188,13 @@
         <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I2" s="12">
         <v>45377</v>
@@ -4220,10 +4211,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>18</v>
@@ -4232,19 +4223,19 @@
         <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I3" s="13">
         <v>45057</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>2</v>
@@ -4255,10 +4246,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
@@ -4267,22 +4258,22 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I4" s="14">
         <v>44810</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
@@ -4290,10 +4281,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>18</v>
@@ -4302,19 +4293,19 @@
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="12">
         <v>45736</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>3</v>
@@ -4325,10 +4316,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
@@ -4337,22 +4328,22 @@
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I6" s="14">
         <v>44816</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -4360,10 +4351,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>18</v>
@@ -4372,22 +4363,22 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" s="12">
         <v>45743</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
@@ -4395,10 +4386,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
@@ -4407,22 +4398,22 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="12">
         <v>45796</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
@@ -4430,10 +4421,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>18</v>
@@ -4442,22 +4433,22 @@
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I9" s="13">
         <v>44569</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
@@ -4465,10 +4456,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>19</v>
@@ -4477,19 +4468,19 @@
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I10" s="14">
         <v>45708</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>4</v>
@@ -4500,10 +4491,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>19</v>
@@ -4512,19 +4503,19 @@
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12">
         <v>45799</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>5</v>
@@ -4535,10 +4526,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>19</v>
@@ -4547,22 +4538,22 @@
         <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I12" s="15">
         <v>45936</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
@@ -4570,10 +4561,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>19</v>
@@ -4582,22 +4573,22 @@
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I13" s="15">
         <v>45936</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
@@ -4605,10 +4596,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>19</v>
@@ -4617,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I14" s="15">
         <v>45708</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>6</v>
@@ -4640,10 +4631,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>19</v>
@@ -4652,19 +4643,19 @@
         <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I15" s="15">
         <v>45796</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>7</v>
@@ -4675,10 +4666,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>19</v>
@@ -4687,22 +4678,22 @@
         <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I16" s="16">
         <v>45736</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -4710,10 +4701,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>19</v>
@@ -4722,22 +4713,22 @@
         <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I17" s="15">
         <v>45922</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -4745,10 +4736,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>19</v>
@@ -4757,22 +4748,22 @@
         <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="J18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -4780,10 +4771,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>19</v>
@@ -4792,22 +4783,22 @@
         <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="J19" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="66" x14ac:dyDescent="0.25">
@@ -4815,10 +4806,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>19</v>
@@ -4827,19 +4818,19 @@
         <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I20" s="17">
         <v>45811</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>8</v>
@@ -4850,10 +4841,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>19</v>
@@ -4862,22 +4853,22 @@
         <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I21" s="15">
         <v>45740</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
@@ -4885,31 +4876,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I22" s="15">
         <v>45657</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>9</v>
@@ -4920,31 +4911,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I23" s="15">
         <v>45573</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>10</v>
@@ -4955,34 +4946,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I24" s="15">
         <v>45657</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
@@ -4990,34 +4981,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I25" s="15">
         <v>44816</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -5025,31 +5016,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I26" s="15">
         <v>45831</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>11</v>
@@ -5060,34 +5051,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I27" s="15">
         <v>45353</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -5095,34 +5086,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I28" s="15">
         <v>45754</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
@@ -5130,31 +5121,31 @@
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I29" s="17">
         <v>45790</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>12</v>
@@ -5165,31 +5156,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I30" s="15">
         <v>45916</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>13</v>
@@ -5200,25 +5191,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I31" s="15">
         <v>45950</v>
@@ -5233,31 +5224,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="G32" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I32" s="15">
         <v>45903</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>13</v>
@@ -5268,31 +5259,31 @@
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I33" s="15">
         <v>45923</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>13</v>
@@ -5303,22 +5294,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H34" s="9"/>
       <c r="I34" s="18"/>
@@ -5330,34 +5321,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G35" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I35" s="15">
         <v>45831</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -5365,34 +5356,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="I36" s="15">
         <v>45353</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -5400,34 +5391,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I37" s="15">
         <v>45740</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -5435,34 +5426,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I38" s="15">
         <v>45657</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -5470,34 +5461,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I39" s="15">
         <v>45831</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -5505,34 +5496,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I40" s="15">
         <v>45353</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -5540,34 +5531,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D41" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="I41" s="15">
         <v>45754</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E790D7B8-DC0A-4A22-8651-060B543F311A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92151698-2544-4259-ADBA-E28A260FF300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-15195" windowWidth="28800" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FR" sheetId="2" r:id="rId1"/>
@@ -3549,9 +3549,6 @@
     <t>Sys/ Sub Sys</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
     <t>65 Armd Regt</t>
   </si>
   <si>
@@ -3577,6 +3574,9 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>Units</t>
   </si>
 </sst>
 </file>
@@ -4144,13 +4144,13 @@
         <v>142</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>22</v>
@@ -4179,7 +4179,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>18</v>
@@ -4214,7 +4214,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>18</v>
@@ -4249,7 +4249,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
@@ -4284,7 +4284,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>18</v>
@@ -4319,7 +4319,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
@@ -4354,7 +4354,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>18</v>
@@ -4389,7 +4389,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
@@ -4424,7 +4424,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>18</v>
@@ -4459,7 +4459,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>19</v>
@@ -4494,7 +4494,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>19</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>19</v>
@@ -4564,7 +4564,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>19</v>
@@ -4599,7 +4599,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>19</v>
@@ -4634,7 +4634,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>19</v>
@@ -4669,7 +4669,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>19</v>
@@ -4704,7 +4704,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>19</v>
@@ -4739,7 +4739,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>19</v>
@@ -4774,7 +4774,7 @@
         <v>25</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>19</v>
@@ -4809,7 +4809,7 @@
         <v>25</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>19</v>
@@ -4844,7 +4844,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>19</v>
@@ -4879,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>19</v>
@@ -4914,7 +4914,7 @@
         <v>25</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>18</v>
@@ -4949,7 +4949,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>18</v>
@@ -4984,7 +4984,7 @@
         <v>25</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>18</v>
@@ -5019,7 +5019,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>18</v>
@@ -5054,7 +5054,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>18</v>
@@ -5089,7 +5089,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>18</v>
@@ -5124,7 +5124,7 @@
         <v>25</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>19</v>
@@ -5159,7 +5159,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>19</v>
@@ -5194,7 +5194,7 @@
         <v>25</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>19</v>
@@ -5209,7 +5209,7 @@
         <v>77</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I31" s="15">
         <v>45950</v>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>67</v>
@@ -5262,7 +5262,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>67</v>
@@ -5297,7 +5297,7 @@
         <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>68</v>
@@ -5324,7 +5324,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>14</v>
@@ -5359,7 +5359,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>14</v>
@@ -5394,7 +5394,7 @@
         <v>25</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>86</v>
@@ -5418,7 +5418,7 @@
         <v>108</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -5429,7 +5429,7 @@
         <v>25</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>86</v>
@@ -5453,7 +5453,7 @@
         <v>108</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -5464,7 +5464,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>18</v>
@@ -5499,7 +5499,7 @@
         <v>25</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>18</v>
@@ -5534,7 +5534,7 @@
         <v>25</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>86</v>
@@ -5558,7 +5558,7 @@
         <v>108</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC967E-7D94-4875-937A-30990647E68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B186B45-E139-4CFE-ACC1-B4771B338357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2265" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -3593,7 +3593,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -3794,31 +3794,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4178,7 +4178,9 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
       <c r="B2" s="9" t="s">
         <v>26</v>
       </c>
@@ -4211,7 +4213,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
       <c r="B3" s="9" t="s">
         <v>26</v>
       </c>
@@ -4244,7 +4248,9 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
       <c r="B4" s="9" t="s">
         <v>26</v>
       </c>
@@ -4277,7 +4283,9 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
       <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
@@ -4310,7 +4318,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
       <c r="B6" s="9" t="s">
         <v>26</v>
       </c>
@@ -4343,7 +4353,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
       <c r="B7" s="9" t="s">
         <v>26</v>
       </c>
@@ -4376,7 +4388,9 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
       <c r="B8" s="9" t="s">
         <v>26</v>
       </c>
@@ -4409,7 +4423,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
       <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
@@ -4442,7 +4458,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
       <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
@@ -4475,7 +4493,9 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
       <c r="B11" s="9" t="s">
         <v>26</v>
       </c>
@@ -4508,7 +4528,9 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
       <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
@@ -4541,7 +4563,9 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
       <c r="B13" s="9" t="s">
         <v>26</v>
       </c>
@@ -4574,7 +4598,9 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>26</v>
       </c>
@@ -4607,7 +4633,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
       <c r="B15" s="9" t="s">
         <v>26</v>
       </c>
@@ -4640,7 +4668,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
       <c r="B16" s="9" t="s">
         <v>26</v>
       </c>
@@ -4673,7 +4703,9 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
       <c r="B17" s="9" t="s">
         <v>26</v>
       </c>
@@ -4706,7 +4738,9 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
       <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
@@ -4739,7 +4773,9 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
       <c r="B19" s="9" t="s">
         <v>26</v>
       </c>
@@ -4772,7 +4808,9 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
       <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
@@ -4805,7 +4843,9 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
       <c r="B21" s="9" t="s">
         <v>26</v>
       </c>
@@ -4838,7 +4878,9 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
       <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
@@ -4871,7 +4913,9 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
       <c r="B23" s="9" t="s">
         <v>26</v>
       </c>
@@ -4904,7 +4948,9 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
       <c r="B24" s="9" t="s">
         <v>26</v>
       </c>
@@ -4937,7 +4983,9 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
       <c r="B25" s="9" t="s">
         <v>26</v>
       </c>
@@ -4970,7 +5018,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
       <c r="B26" s="9" t="s">
         <v>26</v>
       </c>
@@ -5003,7 +5053,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
       <c r="B27" s="9" t="s">
         <v>26</v>
       </c>
@@ -5036,7 +5088,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
       <c r="B28" s="9" t="s">
         <v>26</v>
       </c>
@@ -5069,7 +5123,9 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
       <c r="B29" s="9" t="s">
         <v>26</v>
       </c>
@@ -5102,7 +5158,9 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
       <c r="B30" s="9" t="s">
         <v>26</v>
       </c>
@@ -5135,7 +5193,9 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>26</v>
       </c>
@@ -5166,7 +5226,9 @@
       <c r="K31" s="5"/>
     </row>
     <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
       <c r="B32" s="9" t="s">
         <v>26</v>
       </c>
@@ -5199,7 +5261,9 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
       <c r="B33" s="9" t="s">
         <v>26</v>
       </c>
@@ -5232,7 +5296,9 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
       <c r="B34" s="9" t="s">
         <v>26</v>
       </c>
@@ -5257,7 +5323,9 @@
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
       <c r="B35" s="9" t="s">
         <v>26</v>
       </c>
@@ -5290,7 +5358,9 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
       <c r="B36" s="9" t="s">
         <v>26</v>
       </c>
@@ -5323,7 +5393,9 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
       <c r="B37" s="9" t="s">
         <v>26</v>
       </c>
@@ -5356,7 +5428,9 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -5389,7 +5463,9 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="9"/>
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -5422,7 +5498,9 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="9"/>
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -5455,7 +5533,9 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="9"/>
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
       <c r="B41" s="9" t="s">
         <v>26</v>
       </c>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B186B45-E139-4CFE-ACC1-B4771B338357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E972A467-A0AD-4E0E-B9B0-EFE4E786A532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2265" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="FR" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderLocal_Nov 2025 D.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E972A467-A0AD-4E0E-B9B0-EFE4E786A532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38C2FE0-1276-41A8-8AF3-4C6ECA0353BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FR" sheetId="2" r:id="rId1"/>
+    <sheet name="FR" sheetId="4" r:id="rId1"/>
+    <sheet name="SPARES" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="154">
   <si>
     <t>No</t>
   </si>
@@ -125,18 +126,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Type of Veh</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF050505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Tk BA No</t>
     </r>
   </si>
@@ -3586,6 +3575,9 @@
   </si>
   <si>
     <t>Under FR</t>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -4124,48 +4116,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD5C46C-B07C-42BA-9996-0A0B735859A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B16F41-3B99-4C3D-A695-F6E185BB66E7}">
   <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="8"/>
-    <col min="2" max="2" width="13.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="8" customWidth="1"/>
     <col min="6" max="6" width="18" style="8" customWidth="1"/>
     <col min="7" max="7" width="14" style="8" customWidth="1"/>
     <col min="8" max="8" width="30.6640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="18" style="19" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="67.83203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="8" customWidth="1"/>
+    <col min="11" max="11" width="67.77734375" style="8" customWidth="1"/>
     <col min="12" max="16384" width="9.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>16</v>
@@ -4174,18 +4166,18 @@
         <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>18</v>
@@ -4194,13 +4186,13 @@
         <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I2" s="12">
         <v>45377</v>
@@ -4212,15 +4204,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>18</v>
@@ -4229,33 +4221,33 @@
         <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I3" s="13">
         <v>45057</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
@@ -4264,33 +4256,33 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I4" s="14">
         <v>44810</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>18</v>
@@ -4299,33 +4291,33 @@
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" s="12">
         <v>45736</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
@@ -4334,33 +4326,33 @@
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I6" s="14">
         <v>44816</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>18</v>
@@ -4369,33 +4361,33 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" s="12">
         <v>45743</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
@@ -4404,33 +4396,33 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="12">
         <v>45796</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>18</v>
@@ -4439,33 +4431,33 @@
         <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I9" s="13">
         <v>44569</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>19</v>
@@ -4474,33 +4466,33 @@
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I10" s="14">
         <v>45708</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>19</v>
@@ -4509,33 +4501,33 @@
         <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12">
         <v>45799</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>19</v>
@@ -4544,33 +4536,33 @@
         <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I12" s="15">
         <v>45936</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>19</v>
@@ -4579,33 +4571,33 @@
         <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I13" s="15">
         <v>45936</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>19</v>
@@ -4614,33 +4606,33 @@
         <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I14" s="15">
         <v>45708</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>19</v>
@@ -4649,33 +4641,33 @@
         <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I15" s="15">
         <v>45796</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>19</v>
@@ -4684,33 +4676,33 @@
         <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I16" s="16">
         <v>45736</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>19</v>
@@ -4719,33 +4711,33 @@
         <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I17" s="15">
         <v>45922</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>19</v>
@@ -4754,33 +4746,33 @@
         <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="J18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>121</v>
-      </c>
     </row>
-    <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>19</v>
@@ -4789,33 +4781,33 @@
         <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="J19" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>124</v>
-      </c>
     </row>
-    <row r="20" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="66" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>19</v>
@@ -4824,33 +4816,33 @@
         <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I20" s="17">
         <v>45811</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>19</v>
@@ -4859,363 +4851,363 @@
         <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I21" s="15">
         <v>45740</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I22" s="15">
         <v>45657</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I23" s="15">
         <v>45573</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I24" s="15">
         <v>45657</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I25" s="15">
         <v>44816</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I26" s="15">
         <v>45831</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I27" s="15">
         <v>45353</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I28" s="15">
         <v>45754</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="K28" s="4" t="s">
-        <v>139</v>
-      </c>
     </row>
-    <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I29" s="17">
         <v>45790</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I30" s="15">
         <v>45916</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I31" s="15">
         <v>45950</v>
@@ -5225,346 +5217,405 @@
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="G32" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I32" s="15">
         <v>45903</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I33" s="15">
         <v>45923</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H34" s="9"/>
       <c r="I34" s="18"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G35" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I35" s="15">
         <v>45831</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="I36" s="15">
         <v>45353</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I37" s="15">
         <v>45740</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I38" s="15">
         <v>45657</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I39" s="15">
         <v>45831</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I40" s="15">
         <v>45353</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D41" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="I41" s="15">
         <v>45754</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K41" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD5C46C-B07C-42BA-9996-0A0B735859A2}">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" style="8"/>
+    <col min="2" max="2" width="13.44140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="18" style="8" customWidth="1"/>
+    <col min="7" max="7" width="14" style="8" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="18" style="19" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="8" customWidth="1"/>
+    <col min="11" max="11" width="67.77734375" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9.33203125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>153</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
